--- a/港岛-西营盘及上环-42 Tung St./42 Tung St._销控明细表.xlsx
+++ b/港岛-西营盘及上环-42 Tung St./42 Tung St._销控明细表.xlsx
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -635,10 +635,14 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -696,6 +700,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -742,6 +766,22 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>41652000</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>36000</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>60日付款計劃</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -777,7 +817,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -788,6 +828,22 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>39222300</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>33900</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -818,21 +874,37 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
-        <v>42295000</v>
+        <v>38066000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>36556</v>
+        <v>32901</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>38066000</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>32901</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -869,7 +941,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -880,6 +952,22 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>39223000</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>33901</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -915,7 +1003,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -926,6 +1014,22 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>24238000</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>41503</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -961,7 +1065,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -972,6 +1076,22 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>18783000</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>32163</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1007,7 +1127,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1018,6 +1138,22 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>17412000</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>29815</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1053,7 +1189,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1064,6 +1200,22 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>17154000</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>29373</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1099,7 +1251,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1110,6 +1262,22 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>16574000</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>28380</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1145,7 +1313,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1156,6 +1324,22 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>16330000</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>27962</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1191,7 +1375,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1202,6 +1386,22 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>15932000</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>27281</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1237,7 +1437,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1248,6 +1448,22 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>15393000</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>26358</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1283,7 +1499,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1294,13 +1510,29 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>15393000</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>26358</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -1367,7 +1599,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -1377,7 +1609,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -1429,7 +1661,7 @@
           <t>- | 1157呎 (3房)
 $3922万
 $33,900/呎
-(已售)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1671,12 @@
           <t>17&amp;17U</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>- | 1157呎 (3房)
-$4230万
-$36,556/呎
-(在售)</t>
+$3807万
+$32,901/呎
+(26年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1691,7 @@
           <t>- | 1157呎 (3房)
 $3922万
 $33,901/呎
-(已售)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1706,7 @@
           <t>- | 584呎 (2房)
 $2424万
 $41,503/呎
-(已售)</t>
+(23年-09月-14日)</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1721,7 @@
           <t>- | 584呎 (2房)
 $1878万
 $32,163/呎
-(已售)</t>
+(26年-01月-27日)</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1736,7 @@
           <t>- | 584呎 (2房)
 $1741万
 $29,815/呎
-(已售)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1751,7 @@
           <t>- | 584呎 (2房)
 $1715万
 $29,373/呎
-(已售)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1766,7 @@
           <t>- | 584呎 (2房)
 $1657万
 $28,380/呎
-(已售)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1781,7 @@
           <t>- | 584呎 (2房)
 $1633万
 $27,962/呎
-(已售)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1796,7 @@
           <t>- | 584呎 (2房)
 $1593万
 $27,281/呎
-(已售)</t>
+(26年-01月-16日)</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1811,7 @@
           <t>- | 584呎 (2房)
 $1539万
 $26,358/呎
-(已售)</t>
+(25年-03月-28日)</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1826,7 @@
           <t>- | 584呎 (2房)
 $1539万
 $26,358/呎
-(已售)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
     </row>

--- a/港岛-西营盘及上环-42 Tung St./42 Tung St._销控明细表.xlsx
+++ b/港岛-西营盘及上环-42 Tung St./42 Tung St._销控明细表.xlsx
@@ -879,7 +879,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -1676,7 +1676,7 @@
           <t>- | 1157呎 (3房)
 $3807万
 $32,901/呎
-(26年-07月-13日)</t>
+(26年-08月-04日)</t>
         </is>
       </c>
     </row>

--- a/港岛-西营盘及上环-42 Tung St./42 Tung St._销控明细表.xlsx
+++ b/港岛-西营盘及上环-42 Tung St./42 Tung St._销控明细表.xlsx
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="H3" s="5" t="n">
-        <v>46280000</v>
+        <v>48851000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>40000</v>
+        <v>42222</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>41652000</v>
+        <v>43965900</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>36000</v>
+        <v>38000</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
@@ -1644,8 +1644,8 @@
       <c r="B5" s="20" t="inlineStr">
         <is>
           <t>- | 1157呎 (3房)
-$4628万
-$40,000/呎
+$4885万
+$42,222/呎
 (在售)</t>
         </is>
       </c>
